--- a/src/dataset/인천공항_시간별_이용객수(2026.03).xlsx
+++ b/src/dataset/인천공항_시간별_이용객수(2026.03).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Desktop\대학생활\학연생\Routing\src\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16278508-9899-4078-AAC2-E4E4F9C059EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC840FA-2A80-49C7-BC5E-EF8EEBCA8E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{C0BAC557-57CF-444D-82DB-B9BEF298E675}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="23040" windowHeight="12168" xr2:uid="{C0BAC557-57CF-444D-82DB-B9BEF298E675}"/>
   </bookViews>
   <sheets>
     <sheet name="By_Time_202603_202603" sheetId="1" r:id="rId1"/>
@@ -107,11 +107,11 @@
     <t>23:00 ~ 23:59</t>
   </si>
   <si>
-    <t>Time</t>
+    <t>Normal_Count</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>Normal_Count</t>
+    <t>time</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1143,10 +1143,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
@@ -1245,7 +1245,7 @@
         <v>12293.58064516129</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>11163.225806451614</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>12533</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>12046.516129032258</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
         <v>15</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>13421.612903225807</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>14118.870967741936</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>13370.483870967742</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>10088.612903225807</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>13226.483870967742</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>12660.548387096775</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>11251.032258064517</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>4791.6451612903229</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="31.2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
